--- a/phase3/output/课程标准结构化解析.xlsx
+++ b/phase3/output/课程标准结构化解析.xlsx
@@ -9518,7 +9518,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>岗位全部待核验，课程匹配及图谱语义联系全部待人工审核；文本支撑不等同实际培养</t>
+          <t>历史招聘及关系证据状态保留但不再新增核验任务；当前仅课程能力图谱复核，文本支撑不等同实际培养</t>
         </is>
       </c>
     </row>
